--- a/00. Document/03. 개발문서/든든하이_API명세서(25-0517_은재).xlsx
+++ b/00. Document/03. 개발문서/든든하이_API명세서(25-0517_은재).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\2025_Project\00. Document\03. 개발문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4399ED0-11DE-41C0-8A76-9529B96CC7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6C8FBAA-152F-486F-AB62-A0F7E21E35C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8124" yWindow="252" windowWidth="13800" windowHeight="11652" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
